--- a/Каталог.xlsx
+++ b/Каталог.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\BibCatalog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2F52A198-9679-4C09-82D0-B7086B0F075E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DCE2B6C-CF32-41D2-99E0-15BFF7B3CBDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{72E93EC1-3DCF-4E60-9351-FB1B7C478F0B}"/>
+    <workbookView xWindow="480" yWindow="360" windowWidth="18200" windowHeight="12910" xr2:uid="{72E93EC1-3DCF-4E60-9351-FB1B7C478F0B}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4471" uniqueCount="2160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4471" uniqueCount="2161">
   <si>
     <t>Название</t>
   </si>
@@ -6516,6 +6516,9 @@
   </si>
   <si>
     <t>ШПСА 00608</t>
+  </si>
+  <si>
+    <t>ШПСА 00830</t>
   </si>
 </sst>
 </file>
@@ -8640,7 +8643,7 @@
         <v>78</v>
       </c>
       <c r="G55" s="20" t="s">
-        <v>184</v>
+        <v>2160</v>
       </c>
       <c r="H55" s="7" t="s">
         <v>185</v>
@@ -15562,7 +15565,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="331" spans="1:8" ht="70" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A331" s="33" t="s">
         <v>963</v>
       </c>
